--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3664,291 +3664,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DDFB3ED-F85D-43CA-AAD2-79197E318C5D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F99F5A-0338-4EB4-95D6-3DD37134D590}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9B2FBC7-18C6-423E-8AEF-EE0D3AA0C20E}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3664,4 +3664,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{877A6658-5F99-4F1F-9C75-93F6B450F9C2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AED93641-6724-4EB2-9040-0937C3841B3B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA29C687-4FDC-4AEA-88D5-4632CEB24E0F}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{877A6658-5F99-4F1F-9C75-93F6B450F9C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{474F97E6-8F81-4096-B473-F8029C3198DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AED93641-6724-4EB2-9040-0937C3841B3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{668A7EE0-8A32-4049-B470-FE5A9C2820E3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA29C687-4FDC-4AEA-88D5-4632CEB24E0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{682F4353-6B3D-48F2-BD10-7C0B84ED275C}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{474F97E6-8F81-4096-B473-F8029C3198DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F89F99E-600F-4C65-A66D-E3B595B2F95B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{668A7EE0-8A32-4049-B470-FE5A9C2820E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{837B915C-DCB8-4085-BF4A-716D86ADAFE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{682F4353-6B3D-48F2-BD10-7C0B84ED275C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45AD9BB6-30B5-4847-B57D-8E513B43CB53}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F89F99E-600F-4C65-A66D-E3B595B2F95B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E660A879-90EF-410F-A2FD-47FBE96EDB18}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{837B915C-DCB8-4085-BF4A-716D86ADAFE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0678BAC-20EE-4341-A01B-83F834D356E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45AD9BB6-30B5-4847-B57D-8E513B43CB53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198E7159-FAEE-4EE2-ADB7-2208F5A832F8}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E660A879-90EF-410F-A2FD-47FBE96EDB18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E4BAC3-DBF2-4A0C-A104-63687DE3680F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0678BAC-20EE-4341-A01B-83F834D356E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA5A452-4BD5-43CF-90BB-EA925905A6CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198E7159-FAEE-4EE2-ADB7-2208F5A832F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B79525-E087-4BA6-8C1D-886068257F41}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E4BAC3-DBF2-4A0C-A104-63687DE3680F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3271EC90-9850-4BA4-9776-19E7AC5FEE08}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA5A452-4BD5-43CF-90BB-EA925905A6CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F0921C4-2524-45DF-8550-AFD10405BD20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B79525-E087-4BA6-8C1D-886068257F41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0EB1840-88A4-4CD9-8DE2-8FC4ACE8FB10}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3271EC90-9850-4BA4-9776-19E7AC5FEE08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A75A14-F980-4FA4-A770-B73FE9013EED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F0921C4-2524-45DF-8550-AFD10405BD20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184D64C0-C3EE-4DEE-BD57-36D16C1EBF3A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0EB1840-88A4-4CD9-8DE2-8FC4ACE8FB10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5491CE31-6B17-4525-A924-166A1F2A38AF}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85A75A14-F980-4FA4-A770-B73FE9013EED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233A6CE3-F60B-4EAE-9374-067E7F8F8036}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184D64C0-C3EE-4DEE-BD57-36D16C1EBF3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85397D0-0CCE-420A-8927-FFCE2FA5138A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5491CE31-6B17-4525-A924-166A1F2A38AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00864C49-C359-4F77-96DF-317AA5920769}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{233A6CE3-F60B-4EAE-9374-067E7F8F8036}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0D3B91-91C1-4F08-92D3-A92668779DB5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85397D0-0CCE-420A-8927-FFCE2FA5138A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86A10E4D-1CDF-448F-9953-DEF9446BAB8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00864C49-C359-4F77-96DF-317AA5920769}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D2C67-373C-4692-9C2D-54C7EAF9CAFB}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0D3B91-91C1-4F08-92D3-A92668779DB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED3061E4-A9F3-402E-85B8-A7B73D7E33D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86A10E4D-1CDF-448F-9953-DEF9446BAB8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6EA0F78-2161-4C80-B799-3811FEDD3489}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA2D2C67-373C-4692-9C2D-54C7EAF9CAFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36C700FE-0A31-4E13-8FE3-AE932B5FF55A}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED3061E4-A9F3-402E-85B8-A7B73D7E33D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{721E30E6-3419-4D68-A7A0-7749AED76D6A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6EA0F78-2161-4C80-B799-3811FEDD3489}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A0C761-2011-4A0F-A953-E10CE1DC1E84}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36C700FE-0A31-4E13-8FE3-AE932B5FF55A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3261E5F-2FFF-4172-A506-506EE65F54CB}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{721E30E6-3419-4D68-A7A0-7749AED76D6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8D8AD6-95A8-4351-9304-B9314DDC6304}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A0C761-2011-4A0F-A953-E10CE1DC1E84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D42E47B4-949C-428E-9374-E6A81DC802BD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3261E5F-2FFF-4172-A506-506EE65F54CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43057901-EFB1-41CE-BDCD-067608D8CE7D}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B8D8AD6-95A8-4351-9304-B9314DDC6304}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A8FA6C8-B0E5-4A62-BAFC-2DE3F5C7A761}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D42E47B4-949C-428E-9374-E6A81DC802BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5718E3D-245C-40DC-A46E-915724641FF9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43057901-EFB1-41CE-BDCD-067608D8CE7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F621CB5-B2E6-4B9B-821E-5A87E7272720}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A8FA6C8-B0E5-4A62-BAFC-2DE3F5C7A761}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FBC5167-75E6-4983-9C18-44A44872C584}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5718E3D-245C-40DC-A46E-915724641FF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A75A16B3-041E-40AC-818B-3335ADC964B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F621CB5-B2E6-4B9B-821E-5A87E7272720}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA75BA31-0D83-42C7-8CD3-11263AD4B175}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FBC5167-75E6-4983-9C18-44A44872C584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528F12DD-8EEB-4542-B2C5-35E71657E5AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A75A16B3-041E-40AC-818B-3335ADC964B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFD409AC-0137-4124-AF39-563F4DD43037}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA75BA31-0D83-42C7-8CD3-11263AD4B175}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A529676C-5DB9-4FA5-BCA3-F2B26FC40253}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3664,291 +3664,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{528F12DD-8EEB-4542-B2C5-35E71657E5AC}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFD409AC-0137-4124-AF39-563F4DD43037}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A529676C-5DB9-4FA5-BCA3-F2B26FC40253}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3664,4 +3664,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13807E18-AD86-4DD2-8B08-6E71CCBC2078}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA3E44E-DDD8-42F4-A74A-64CB247AA4CD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11BDDBC1-A78C-43AE-A2CD-CCF0E37591C9}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13807E18-AD86-4DD2-8B08-6E71CCBC2078}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341D7F34-A73F-4CD5-9BB2-1096C860CDC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BA3E44E-DDD8-42F4-A74A-64CB247AA4CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76655ED-FE9A-4D35-A189-18FFAA0F0F3C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11BDDBC1-A78C-43AE-A2CD-CCF0E37591C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68B9A53E-B420-4746-927E-947D3BD8F443}"/>
 </file>
--- a/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
+++ b/Seymour_etal_2017/Seymour_etal_2017_TableS1_snapshot.xlsx
@@ -3942,13 +3942,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{341D7F34-A73F-4CD5-9BB2-1096C860CDC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3AD2D32-78CC-4CF4-B8C1-4B9D29CF8EC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76655ED-FE9A-4D35-A189-18FFAA0F0F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D31CD8-552A-46DE-A9F7-DD3E5A3A425C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68B9A53E-B420-4746-927E-947D3BD8F443}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B329F4F-CE1C-48B8-9529-CD7C1995C005}"/>
 </file>